--- a/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,33</t>
+          <t>0,0; 27,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,4</t>
+          <t>0,0; 40,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 16,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 12,85</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 29,37</t>
+          <t>4,29; 29,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,11</t>
+          <t>0,0; 17,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 23,8</t>
+          <t>2,51; 25,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,95</t>
+          <t>0,0; 24,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,81</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,51</t>
+          <t>1,33; 13,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 19,98</t>
+          <t>4,19; 20,3</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,94</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,18</t>
+          <t>0,0; 24,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,83</t>
+          <t>0,0; 44,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,35</t>
+          <t>0,0; 25,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 25,85</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 17,23</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,37</t>
+          <t>0,0; 44,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,51</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,63</t>
+          <t>0,0; 48,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 26,66</t>
+          <t>3,86; 29,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,68</t>
+          <t>0,0; 25,02</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,28</t>
+          <t>2,09; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,2</t>
+          <t>1,47; 12,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,3</t>
+          <t>2,36; 13,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,71</t>
+          <t>2,75; 16,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,57; 8,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,49</t>
+          <t>1,81; 8,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,0</t>
+          <t>3,57; 11,51</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2514</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2994</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3115</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2475</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>974; 6724</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3459</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>630; 6296</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4446</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3093</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>603; 5937</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1716; 8319</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3898</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3006</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4445</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3596</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5953</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4493</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4061</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4277</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3994</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>929; 7016</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4173</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7146</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4230</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4015</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1151; 7592</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685; 5818</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1499; 8841</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1318; 7746</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1426; 7980</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2255; 10719</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3680; 11856</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,53</t>
+          <t>0,0; 27,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,49</t>
+          <t>0,0; 35,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,88</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 15,39</t>
         </is>
       </c>
     </row>
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 29,59</t>
+          <t>4,59; 26,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,63</t>
+          <t>0,0; 18,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 25,07</t>
+          <t>2,42; 23,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,36</t>
+          <t>0,0; 24,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 11,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,09</t>
+          <t>1,35; 13,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 20,3</t>
+          <t>4,04; 20,95</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 29,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,99</t>
+          <t>0,0; 25,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,59</t>
+          <t>0,0; 43,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 24,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,74</t>
+          <t>3,32; 26,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,23</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,76</t>
+          <t>0,0; 45,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,54</t>
+          <t>0,0; 33,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,88</t>
+          <t>0,0; 42,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 29,16</t>
+          <t>2,95; 27,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,02</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,64</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,77</t>
+          <t>2,18; 13,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,46</t>
+          <t>1,47; 11,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,91</t>
+          <t>1,96; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 16,18</t>
+          <t>2,68; 14,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,81</t>
+          <t>1,44; 8,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,59</t>
+          <t>1,75; 7,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,51</t>
+          <t>3,59; 11,61</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2514</t>
+          <t>0; 2513</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2994</t>
+          <t>0; 2623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3115</t>
+          <t>0; 2612</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2475</t>
+          <t>0; 2964</t>
         </is>
       </c>
     </row>
@@ -1590,37 +1590,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>974; 6724</t>
+          <t>1043; 6102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>630; 6296</t>
+          <t>608; 5786</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4446</t>
+          <t>0; 4381</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>603; 5937</t>
+          <t>613; 6172</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1716; 8319</t>
+          <t>1654; 8583</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3898</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3006</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>0; 4322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3596</t>
+          <t>0; 3436</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5953</t>
+          <t>687; 5575</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4107</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4277</t>
+          <t>0; 4963</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3994</t>
+          <t>0; 3458</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>929; 7016</t>
+          <t>711; 6612</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4173</t>
+          <t>0; 3894</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4230</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4015</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1151; 7592</t>
+          <t>1200; 7458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>685; 5818</t>
+          <t>686; 5499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1499; 8841</t>
+          <t>1248; 8726</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1318; 7746</t>
+          <t>1284; 7162</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1426; 7980</t>
+          <t>1306; 7770</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2255; 10719</t>
+          <t>2181; 9965</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3680; 11856</t>
+          <t>3701; 11959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,15</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,39</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,47; 23,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 26,85</t>
+          <t>0,0; 24,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 23,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,01</t>
+          <t>3,02; 29,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,18</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,61</t>
+          <t>1,35; 13,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 20,95</t>
+          <t>4,0; 19,98</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,96</t>
+          <t>0,0; 41,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,2</t>
+          <t>0,0; 21,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,36</t>
+          <t>0,0; 29,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,46</t>
+          <t>0,0; 20,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 26,92</t>
+          <t>3,24; 25,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,75</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14,91%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,96</t>
+          <t>0,0; 30,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,12</t>
+          <t>0,0; 42,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 27,48</t>
+          <t>2,93; 26,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 23,68</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>1,44; 12,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>2,18; 14,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,53</t>
+          <t>2,7; 15,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,77</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 13,73</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,96</t>
+          <t>2,05; 13,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,58</t>
+          <t>1,52; 8,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,98</t>
+          <t>1,94; 8,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,61</t>
+          <t>3,68; 12,0</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,24 +1364,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2623</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2612</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2964</t>
+          <t>0; 2894</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>2824</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>620; 5977</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1043; 6102</t>
+          <t>0; 4554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3724</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>608; 5786</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4381</t>
+          <t>686; 6673</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>613; 6172</t>
+          <t>612; 6126</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1654; 8583</t>
+          <t>1639; 8185</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1487</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 4170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 2998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 3217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>0; 2428</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>687; 5575</t>
+          <t>672; 5353</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 3880</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1858,27 +1858,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 4572</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3458</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>711; 6612</t>
+          <t>706; 6414</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3949</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3388</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4251</t>
+          <t>674; 5700</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>1385; 9087</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1200; 7458</t>
+          <t>1293; 7517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>686; 5499</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1248; 8726</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1284; 7162</t>
+          <t>1129; 7318</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1306; 7770</t>
+          <t>1378; 7981</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2181; 9965</t>
+          <t>2418; 10596</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3701; 11959</t>
+          <t>3787; 12362</t>
         </is>
       </c>
     </row>
